--- a/tests/testdata/excel/ファイル名/100%.xlsx
+++ b/tests/testdata/excel/ファイル名/100%.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\test\AppData\Local\Temp\win_grep_testdata\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{498C7941-8536-4CE5-B7A2-6FC804A1B90F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A8874442-9FCF-4612-8333-F59DAD1F0670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{2399BE2E-DEF1-4264-90AD-D9B18E07F2BC}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="10515" xr2:uid="{13A94E27-FAF8-48BA-9020-ED25D2846B43}"/>
   </bookViews>
   <sheets>
     <sheet name="100%" sheetId="1" r:id="rId1"/>
@@ -433,7 +433,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59DBF6BA-3B3C-44A8-9A58-F64167B05237}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB76C6C2-245F-4B68-9AEC-2D991A310C10}">
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <sheetData>
